--- a/excel-files/LAS PINAS/ILAYA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/ILAYA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0B775A8-2C04-4B8F-B7D1-F9FB8E093174}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA760614-83EB-47DD-AF17-04F6A97ED445}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -628,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -756,6 +756,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3039,8 +3042,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
-  <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA132" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+  <autoFilter ref="A2:AA132" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
     <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
@@ -5452,7 +5455,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA162"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -9537,7 +9540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9606,7 +9609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9675,7 +9678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9744,7 +9747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9813,7 +9816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9882,7 +9885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9951,7 +9954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -10020,7 +10023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10172,7 +10175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10241,7 +10244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10310,7 +10313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10379,7 +10382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10448,7 +10451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10517,7 +10520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10586,7 +10589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10655,7 +10658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10807,7 +10810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10876,7 +10879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10945,7 +10948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -11014,7 +11017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11083,7 +11086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11152,7 +11155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11221,7 +11224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11290,7 +11293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11442,7 +11445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11511,7 +11514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11580,7 +11583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11649,7 +11652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11718,7 +11721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11787,7 +11790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11856,7 +11859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11925,7 +11928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12008,7 +12011,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -12077,7 +12080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -12146,7 +12149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12215,7 +12218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12284,7 +12287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12353,7 +12356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12422,7 +12425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12491,7 +12494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12571,7 +12574,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12633,7 +12636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12695,7 +12698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12757,7 +12760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12819,7 +12822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12881,7 +12884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12943,7 +12946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13005,7 +13008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13067,7 +13070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13129,7 +13132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13191,7 +13194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13253,7 +13256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13315,7 +13318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13377,7 +13380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13439,7 +13442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13501,7 +13504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13522,7 +13525,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13534,7 +13537,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13549,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13560,191 +13563,336 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
+    <row r="128" spans="1:27" ht="19.5">
+      <c r="A128" s="32"/>
+      <c r="B128" s="33"/>
+      <c r="C128" s="32"/>
+      <c r="D128" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E128" s="34"/>
+      <c r="F128" s="32"/>
+      <c r="G128" s="34"/>
+      <c r="H128" s="46">
+        <f t="shared" ref="H128:H132" si="26">IF((D128-E128)&lt;0,0,(D128-E128))</f>
+        <v>0</v>
+      </c>
+      <c r="I128" s="46">
+        <f t="shared" ref="I128:I132" si="27">IF((E128-D128)&lt;0,0,(E128-D128))</f>
+        <v>0</v>
+      </c>
+      <c r="J128" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K128" s="34"/>
+      <c r="L128" s="1"/>
+      <c r="M128" s="34"/>
+      <c r="N128" s="34"/>
+      <c r="O128" s="34"/>
+      <c r="P128" s="34" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
+      <c r="Q128" s="34"/>
+      <c r="R128" s="1"/>
+      <c r="S128" s="34"/>
+      <c r="T128" s="34" t="e">
+        <f t="shared" ref="T128:T132" si="28">IF((P128-Q128)&lt;0,0,(P128-Q128))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U128" s="34" t="e">
+        <f t="shared" ref="U128:U132" si="29">IF((Q128-P128)&lt;0,0,(Q128-P128))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="V128" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W128" s="34"/>
+      <c r="X128" s="1"/>
+      <c r="Y128" s="34"/>
+      <c r="Z128" s="34">
+        <f t="shared" ref="Z128:Z132" si="30">IF((V128-W128)&lt;0,0,(V128-W128))</f>
+        <v>0</v>
+      </c>
+      <c r="AA128" s="34">
+        <f t="shared" ref="AA128:AA132" si="31">IF((W128-V128)&lt;0,0,(W128-V128))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:27" ht="19.5">
+      <c r="A129" s="32"/>
+      <c r="B129" s="33"/>
+      <c r="C129" s="32"/>
+      <c r="D129" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E129" s="34"/>
+      <c r="F129" s="32"/>
+      <c r="G129" s="34"/>
+      <c r="H129" s="46">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="I129" s="46">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J129" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K129" s="34"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="34"/>
+      <c r="N129" s="34"/>
+      <c r="O129" s="34"/>
+      <c r="P129" s="34" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
+      <c r="Q129" s="34"/>
+      <c r="R129" s="1"/>
+      <c r="S129" s="34"/>
+      <c r="T129" s="34" t="e">
+        <f t="shared" si="28"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U129" s="34" t="e">
+        <f t="shared" si="29"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V129" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W129" s="34"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="34"/>
+      <c r="Z129" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AA129" s="34">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:27" ht="19.5">
+      <c r="A130" s="32"/>
+      <c r="B130" s="33"/>
+      <c r="C130" s="32"/>
+      <c r="D130" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E130" s="34"/>
+      <c r="F130" s="32"/>
+      <c r="G130" s="34"/>
+      <c r="H130" s="46">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="I130" s="46">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J130" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K130" s="34"/>
+      <c r="L130" s="1"/>
+      <c r="M130" s="34"/>
+      <c r="N130" s="34"/>
+      <c r="O130" s="34"/>
+      <c r="P130" s="34" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
+      <c r="Q130" s="34"/>
+      <c r="R130" s="1"/>
+      <c r="S130" s="34"/>
+      <c r="T130" s="34" t="e">
+        <f t="shared" si="28"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U130" s="34" t="e">
+        <f t="shared" si="29"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V130" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W130" s="34"/>
+      <c r="X130" s="1"/>
+      <c r="Y130" s="34"/>
+      <c r="Z130" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AA130" s="34">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:27" ht="19.5">
+      <c r="A131" s="32"/>
+      <c r="B131" s="33"/>
+      <c r="C131" s="32"/>
+      <c r="D131" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E131" s="34"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="34"/>
+      <c r="H131" s="46">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="I131" s="46">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J131" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K131" s="34"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="34"/>
+      <c r="N131" s="34"/>
+      <c r="O131" s="34"/>
+      <c r="P131" s="34" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
+      <c r="Q131" s="34"/>
+      <c r="R131" s="1"/>
+      <c r="S131" s="34"/>
+      <c r="T131" s="34" t="e">
+        <f t="shared" si="28"/>
+        <v>#REF!</v>
+      </c>
+      <c r="U131" s="34" t="e">
+        <f t="shared" si="29"/>
+        <v>#REF!</v>
+      </c>
+      <c r="V131" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W131" s="34"/>
+      <c r="X131" s="1"/>
+      <c r="Y131" s="34"/>
+      <c r="Z131" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AA131" s="34">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:27" ht="19.5">
+      <c r="A132" s="32"/>
+      <c r="B132" s="33"/>
+      <c r="C132" s="32"/>
+      <c r="D132" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E132" s="34"/>
+      <c r="F132" s="32"/>
+      <c r="G132" s="34"/>
+      <c r="H132" s="46">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="I132" s="46">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J132" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K132" s="34"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="34"/>
+      <c r="N132" s="34"/>
+      <c r="O132" s="34"/>
+      <c r="P132" s="34" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
+      <c r="Q132" s="34"/>
+      <c r="R132" s="1"/>
+      <c r="S132" s="34"/>
+      <c r="T132" s="34" t="e">
+        <f t="shared" si="28"/>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
+      <c r="U132" s="34" t="e">
+        <f t="shared" si="29"/>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
+      <c r="V132" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W132" s="34"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="34"/>
+      <c r="Z132" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AA132" s="34">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:27" ht="15"/>
+    <row r="134" spans="1:27" ht="15"/>
+    <row r="135" spans="1:27" ht="15"/>
+    <row r="136" spans="1:27" ht="15"/>
+    <row r="137" spans="1:27" ht="15"/>
+    <row r="138" spans="1:27" ht="15"/>
+    <row r="139" spans="1:27" ht="15"/>
+    <row r="140" spans="1:27" ht="15"/>
+    <row r="141" spans="1:27" ht="15"/>
+    <row r="142" spans="1:27" ht="15"/>
+    <row r="143" spans="1:27" ht="15"/>
+    <row r="144" spans="1:27" ht="15"/>
+    <row r="145" ht="15"/>
+    <row r="146" ht="15"/>
+    <row r="147" ht="15"/>
+    <row r="148" ht="15"/>
+    <row r="149" ht="15"/>
+    <row r="150" ht="15"/>
+    <row r="151" ht="15"/>
+    <row r="152" ht="15"/>
+    <row r="153" ht="15"/>
+    <row r="154" ht="15"/>
+    <row r="155" ht="15"/>
+    <row r="156" ht="15"/>
+    <row r="157" ht="15"/>
+    <row r="158" ht="15"/>
+    <row r="159" ht="15"/>
+    <row r="160" ht="15"/>
+    <row r="161" ht="15"/>
+    <row r="162" ht="15"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="C2:C3 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C132" name="Textbooks"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 D23:F31 D33:F41 H33:I41 D43:F51 H43:I51 D53:F61 H53:I61 D63:F71 H63:I71 D73:F81 H73:I81 D83:F91 H83:I91 D93:F101 H93:I101 D103:F110 H103:I110 H112:I127 W112:X112 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N4:P4 T4:V4 J4 N3:R3 Y13 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 Z4:AA132 T128:W132 N127:Q132 H128:J132 D112:F132 K112:L132 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 Q113:Q126 R113:R132 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W63:X71 W73:X81 W83:X91 W93:X101 W103:X110 W113:W127 X113:X132" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 Y112:Y132 S112:S132 M112:M132 G112:G132" name="SOURCE"/>
     <protectedRange sqref="C5:C12" name="Textbooks_1"/>
     <protectedRange sqref="C14:C21" name="Textbooks_1_1"/>
     <protectedRange sqref="C23:C31" name="Textbooks_2"/>
@@ -13759,15 +13907,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S132 M112:M132 Y112:Y132 G112:G132" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43:F51 F63:F71 F112:F132 F53:F61 F5:F12 F93:F101 F14:F21 F83:F91 F23:F31 F103:F110 F73:F81 F33:F41" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110" xr:uid="{686A25B4-B9D7-4F7D-B6A7-A2E95C75B7B1}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L112:L132 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R132 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110 X112:X132" xr:uid="{F5179D1C-08DC-46BA-A10C-C856CBB8EAA9}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18295,7 +18449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18364,7 +18518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18433,7 +18587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18502,7 +18656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18571,7 +18725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18640,7 +18794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18709,7 +18863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18778,7 +18932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18847,7 +19001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18916,7 +19070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -19055,7 +19209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -19124,7 +19278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -19193,7 +19347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -19262,7 +19416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -19331,7 +19485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19400,7 +19554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19469,7 +19623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19538,7 +19692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19607,7 +19761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19676,7 +19830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19815,7 +19969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19884,7 +20038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19953,7 +20107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -20022,7 +20176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -20091,7 +20245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -20160,7 +20314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -20229,7 +20383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -20298,7 +20452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20367,7 +20521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20436,7 +20590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20575,7 +20729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20644,7 +20798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20713,7 +20867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20782,7 +20936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20851,7 +21005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20920,7 +21074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20989,7 +21143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -21058,7 +21212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -21127,7 +21281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -21196,7 +21350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -21335,7 +21489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -21404,7 +21558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -21473,7 +21627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21542,7 +21696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21611,7 +21765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21680,7 +21834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21749,7 +21903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -22512,7 +22666,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D103:F113 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H103:L113 H115:L122 P2:R10 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 N115:R122 V2:X10 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T67:X77 T79:X89 T91:X101 T103:X113 T115:X122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22522,12 +22676,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F103:F113 F67:F77 F79:F89 F115:F122 F3:F10 F55:F65 F91:F101 F12:F19 F21:F29 F43:F53 F31:F41" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X122" xr:uid="{79D55151-3AE0-43F3-ACA5-BC16E5EA8714}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
